--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/측정결과/xd04_led_cont_bd_불량.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/측정결과/xd04_led_cont_bd_불량.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\측정결과\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BD6E75-7497-45BD-8CE9-55E46CC09E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1259BD01-114B-41B2-AEDA-C7EEE23E6CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{05E4FB0B-4198-4436-B9B1-FD991BA2384A}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{05E4FB0B-4198-4436-B9B1-FD991BA2384A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/측정결과/xd04_led_cont_bd_불량.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/측정결과/xd04_led_cont_bd_불량.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\측정결과\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1259BD01-114B-41B2-AEDA-C7EEE23E6CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6869BE20-06F1-452D-A872-277D31D127B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{05E4FB0B-4198-4436-B9B1-FD991BA2384A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{05E4FB0B-4198-4436-B9B1-FD991BA2384A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="81">
   <si>
     <t>접수 번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -171,6 +172,138 @@
   </si>
   <si>
     <t>불량 XC 채널</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접수 #3</t>
+  </si>
+  <si>
+    <t>접수 #4</t>
+  </si>
+  <si>
+    <t>접수 #5</t>
+  </si>
+  <si>
+    <t>BOARD TEST</t>
+  </si>
+  <si>
+    <t>SPEC</t>
+  </si>
+  <si>
+    <t>BOARD 1</t>
+  </si>
+  <si>
+    <t>BOARD 2</t>
+  </si>
+  <si>
+    <t>BOARD 3</t>
+  </si>
+  <si>
+    <t>BOARD 4</t>
+  </si>
+  <si>
+    <t>BOARD 5</t>
+  </si>
+  <si>
+    <t>TP 1</t>
+  </si>
+  <si>
+    <t>12V</t>
+  </si>
+  <si>
+    <t>12.3V</t>
+  </si>
+  <si>
+    <t>12.2V</t>
+  </si>
+  <si>
+    <t>TP 2</t>
+  </si>
+  <si>
+    <t>9V</t>
+  </si>
+  <si>
+    <t>8.99V</t>
+  </si>
+  <si>
+    <t>3V</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>5.6V</t>
+  </si>
+  <si>
+    <t>TP 3</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>4.99V</t>
+  </si>
+  <si>
+    <t>2V</t>
+  </si>
+  <si>
+    <t>4.97V</t>
+  </si>
+  <si>
+    <t>4.6V</t>
+  </si>
+  <si>
+    <t>TP 4</t>
+  </si>
+  <si>
+    <t>3.3V</t>
+  </si>
+  <si>
+    <t>1.1V</t>
+  </si>
+  <si>
+    <t>TP28</t>
+  </si>
+  <si>
+    <t>780kHz</t>
+  </si>
+  <si>
+    <t>정상</t>
+  </si>
+  <si>
+    <t>비정상</t>
+  </si>
+  <si>
+    <t>BAR 점등</t>
+  </si>
+  <si>
+    <t>점등안됨</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>루멘스 검토 결과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GT 검토 결과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접수 #1 (TL431)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접수 #2 (NCV7809)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.972 ????</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -178,7 +311,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,8 +327,32 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,13 +371,80 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -229,7 +453,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -238,6 +462,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1958,4 +2212,522 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4F36E1-0D47-4FAA-9687-2317A1E4F511}">
+  <dimension ref="A2:AD20"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="19" width="8.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="30" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.6640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="B15" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD15" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="B16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="3">
+        <v>8.98</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.9779999999999998</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4.9770000000000003</v>
+      </c>
+      <c r="G16" s="3">
+        <v>4.9560000000000004</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.504</v>
+      </c>
+      <c r="I16" s="3">
+        <v>787</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30" x14ac:dyDescent="0.45">
+      <c r="B17" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="3">
+        <v>8.9779999999999998</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5.0449999999999999</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.306</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4.9790000000000001</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4.9610000000000003</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1.502</v>
+      </c>
+      <c r="I17" s="3">
+        <v>792</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30" x14ac:dyDescent="0.45">
+      <c r="B18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="3">
+        <v>9.0250000000000004</v>
+      </c>
+      <c r="D18" s="3">
+        <v>4.9729999999999999</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3.3130000000000002</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="I18" s="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="19" spans="2:30" x14ac:dyDescent="0.45">
+      <c r="B19" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30" x14ac:dyDescent="0.45">
+      <c r="B20" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>